--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260203_202514.xlsx
@@ -2930,7 +2930,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
